--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484819_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484819_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8809</v>
+        <v>5.8255</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6391</v>
+        <v>3.4514</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2418</v>
+        <v>2.3741</v>
       </c>
       <c r="G2" t="n">
         <v>4.6707</v>
@@ -610,13 +610,13 @@
         <v>2.6418</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8141</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9792</v>
+        <v>0.7914</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1651</v>
+        <v>-0.0328</v>
       </c>
       <c r="V2" t="n">
         <v>-1.3021</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MUÑOZ PALENCIA</t>
+          <t>S. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.317</v>
+        <v>0.694</v>
       </c>
       <c r="E3" t="n">
-        <v>0.317</v>
+        <v>-1.6642</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2.3582</v>
       </c>
       <c r="G3" t="n">
-        <v>0.317</v>
+        <v>-1.8788</v>
       </c>
       <c r="H3" t="n">
-        <v>0.317</v>
+        <v>1.6419</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-3.5207</v>
       </c>
       <c r="J3" t="n">
-        <v>0.317</v>
+        <v>-1.2924</v>
       </c>
       <c r="K3" t="n">
-        <v>0.317</v>
+        <v>1.8391</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-3.1315</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0.5864</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.1972</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.3892</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.0192</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.389</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.3145</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0.0746</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.7166</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.7166</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. TUDELA GARCIA</t>
+          <t>J. MUÑOZ PALENCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0882</v>
+        <v>0.317</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2725</v>
+        <v>0.317</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1842</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5666</v>
+        <v>0.317</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4954</v>
+        <v>0.317</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0712</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1977</v>
+        <v>0.317</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0743</v>
+        <v>0.317</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1234</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7643</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5697</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1946</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5096</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5096</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3338</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7729</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5609</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.1886</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0034</v>
+        <v>0.2431</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.5606</v>
+        <v>-2.5589</v>
       </c>
       <c r="F5" t="n">
-        <v>2.564</v>
+        <v>2.802</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2214</v>
@@ -844,13 +844,13 @@
         <v>2.4531</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0394</v>
+        <v>0.2003</v>
       </c>
       <c r="T5" t="n">
-        <v>0.148</v>
+        <v>0.1497</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1875</v>
+        <v>0.0506</v>
       </c>
       <c r="V5" t="n">
         <v>0.6415999999999999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3574</v>
+        <v>0.2016</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2694</v>
+        <v>0.4844</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6268</v>
+        <v>-0.2829</v>
       </c>
       <c r="G6" t="n">
         <v>0.1317</v>
@@ -922,13 +922,13 @@
         <v>1.3209</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2063</v>
+        <v>-0.6474</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5139</v>
+        <v>-0.2988</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6925</v>
+        <v>-0.3485</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6036</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. VAL GUTIERREZ</t>
+          <t>K. FEDOROV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4806</v>
+        <v>-0.5812</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9712</v>
+        <v>-0.3909</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4905</v>
+        <v>-0.1903</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8788</v>
+        <v>0.1241</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6419</v>
+        <v>0.1542</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.5207</v>
+        <v>-0.0301</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2924</v>
+        <v>0.8884</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8391</v>
+        <v>0.7239</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.1315</v>
+        <v>0.1645</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5864</v>
+        <v>-0.7643</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1972</v>
+        <v>-0.5697</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3892</v>
+        <v>-0.1946</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R7" t="n">
-        <v>3.0192</v>
+        <v>1.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5637</v>
+        <v>-0.4981</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.6214</v>
+        <v>-0.3359</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0577</v>
+        <v>-0.1622</v>
       </c>
       <c r="V7" t="n">
-        <v>3.7166</v>
+        <v>-0.5846</v>
       </c>
       <c r="W7" t="n">
-        <v>3.7166</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5846</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9204</v>
+        <v>-0.8616</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3687</v>
+        <v>0.4275</v>
       </c>
       <c r="F8" t="n">
         <v>-1.2892</v>
@@ -1078,10 +1078,10 @@
         <v>0.5661</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4609</v>
+        <v>0.5196</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2968</v>
+        <v>0.3556</v>
       </c>
       <c r="U8" t="n">
         <v>0.164</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. FEDOROV</t>
+          <t>G. TUDELA GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,31 +1111,31 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2859</v>
+        <v>-1.0801</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9369</v>
+        <v>0.4745</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.349</v>
+        <v>-1.5546</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1241</v>
+        <v>-0.5666</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1542</v>
+        <v>-0.4954</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0301</v>
+        <v>-0.0712</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8884</v>
+        <v>0.1977</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7239</v>
+        <v>0.0743</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1645</v>
+        <v>0.1234</v>
       </c>
       <c r="M9" t="n">
         <v>-0.7643</v>
@@ -1147,31 +1147,31 @@
         <v>-0.1946</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3774</v>
+        <v>1.5096</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2027</v>
+        <v>0.1655</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8818</v>
+        <v>-0.025</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3209</v>
+        <v>0.1905</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5846</v>
+        <v>-2.1886</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5846</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5388</v>
+        <v>-1.4078</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.586</v>
+        <v>-1.1374</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0471</v>
+        <v>-0.2703</v>
       </c>
       <c r="G10" t="n">
         <v>1.8941</v>
@@ -1234,13 +1234,13 @@
         <v>2.4531</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0576</v>
+        <v>0.1887</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3375</v>
+        <v>0.111</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3951</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2262</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.4693</v>
+        <v>-9.643700000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.1209</v>
+        <v>-9.2424</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3484</v>
+        <v>-0.4013</v>
       </c>
       <c r="G11" t="n">
         <v>-6.1512</v>
@@ -1312,13 +1312,13 @@
         <v>2.6418</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4127</v>
+        <v>0.413</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.913</v>
+        <v>-0.0345</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5004</v>
+        <v>0.4474</v>
       </c>
       <c r="V11" t="n">
         <v>-2.7732</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.762900000000002</v>
+        <v>-6.293200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.3089</v>
+        <v>-9.839</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5458</v>
+        <v>3.5457</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3826</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9487</v>
+        <v>1.948699999999999</v>
       </c>
       <c r="I12" t="n">
         <v>-4.3315</v>
@@ -1369,7 +1369,7 @@
         <v>7.732</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.684400000000001</v>
+        <v>-3.6844</v>
       </c>
       <c r="M12" t="n">
         <v>-6.430099999999999</v>
@@ -1390,28 +1390,28 @@
         <v>17.9265</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7583999999999997</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0707</v>
+        <v>0.399</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3120999999999998</v>
+        <v>0.3121000000000002</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.565300000000001</v>
+        <v>-5.5653</v>
       </c>
       <c r="W12" t="n">
         <v>2.6973</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.262600000000001</v>
+        <v>-8.262599999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. GARCIA RUIZ</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5148</v>
+        <v>2.3313</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0095</v>
+        <v>3.4524</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5243</v>
+        <v>-1.1211</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6935</v>
+        <v>-0.1804</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0203</v>
+        <v>-0.5165</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6731</v>
+        <v>0.3361</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1312</v>
+        <v>1.0884</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1268</v>
+        <v>0.8827</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.258</v>
+        <v>0.2057</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4378</v>
+        <v>-1.2688</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1471</v>
+        <v>-1.3993</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5849</v>
+        <v>0.1304</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9435</v>
+        <v>2.6418</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7178</v>
+        <v>0.4926</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2163</v>
+        <v>0.1945</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.2981</v>
       </c>
       <c r="V13" t="n">
-        <v>1.547</v>
+        <v>0.3208</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9054</v>
+        <v>3.113</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6415999999999999</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>J. DE YRAOLAGOTIA TELLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3289</v>
+        <v>2.2773</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8421</v>
+        <v>-1.0005</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5132</v>
+        <v>3.2778</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1804</v>
+        <v>0.9052</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5165</v>
+        <v>0.0415</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3361</v>
+        <v>0.8637</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0884</v>
+        <v>0.9563</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8827</v>
+        <v>0.8726</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2057</v>
+        <v>0.0837</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2688</v>
+        <v>-0.0511</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3993</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1304</v>
+        <v>0.78</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6983</v>
+        <v>0.5661</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6418</v>
+        <v>2.4531</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4903</v>
+        <v>0.1834</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5842000000000001</v>
+        <v>-0.3716</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.094</v>
+        <v>0.555</v>
       </c>
       <c r="V14" t="n">
+        <v>0.6226</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="X14" t="n">
         <v>0.3208</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.113</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-2.7922</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. DE YRAOLAGOTIA TELLO</t>
+          <t>A. GARCIA RUIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.813</v>
+        <v>2.0554</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.3902</v>
+        <v>-0.2044</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2032</v>
+        <v>2.2598</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9052</v>
+        <v>-0.6935</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0415</v>
+        <v>-0.0203</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8637</v>
+        <v>-0.6731</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9563</v>
+        <v>-1.1312</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8726</v>
+        <v>0.1268</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0837</v>
+        <v>-1.258</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0511</v>
+        <v>0.4378</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.1471</v>
       </c>
       <c r="O15" t="n">
-        <v>0.78</v>
+        <v>0.5849</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4531</v>
+        <v>0.9435</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2809</v>
+        <v>0.2584</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7613</v>
+        <v>0.0214</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4804</v>
+        <v>0.237</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6226</v>
+        <v>1.547</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3018</v>
+        <v>0.9054</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3208</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8092</v>
+        <v>1.9716</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1258</v>
+        <v>0.0283</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6834</v>
+        <v>1.9432</v>
       </c>
       <c r="G16" t="n">
         <v>2.5423</v>
@@ -1702,13 +1702,13 @@
         <v>2.6418</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3992</v>
+        <v>0.5616</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0646</v>
+        <v>-0.0329</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3346</v>
+        <v>0.5944</v>
       </c>
       <c r="V16" t="n">
         <v>0.9434</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LÓPEZ</t>
+          <t>V. BERENGUER DEL VALLE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9339</v>
+        <v>1.0375</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9339</v>
+        <v>0.4285</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.609</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9339</v>
+        <v>1.1264</v>
       </c>
       <c r="H17" t="n">
-        <v>0.317</v>
+        <v>-0.1596</v>
       </c>
       <c r="I17" t="n">
-        <v>0.617</v>
+        <v>1.2861</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9339</v>
+        <v>0.7426</v>
       </c>
       <c r="K17" t="n">
-        <v>0.317</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.617</v>
+        <v>0.6581</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.3838</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.2442</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.628</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.4663</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.3141</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0.1522</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>J. GONZALEZ LÓPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8823</v>
+        <v>0.9339</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9796</v>
+        <v>0.9339</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8619</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3855</v>
+        <v>0.9339</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.6156</v>
+        <v>0.317</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2301</v>
+        <v>0.617</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2736</v>
+        <v>0.9339</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.2649</v>
+        <v>0.317</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9913</v>
+        <v>0.617</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1119</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3507</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2388</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.774</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.8305</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0417</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5966</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4451</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1696</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4714</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. BERENGUER DEL VALLE</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.625</v>
+        <v>0.5143</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3311</v>
+        <v>-1.3693</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2939</v>
+        <v>1.8836</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1264</v>
+        <v>-1.3855</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1596</v>
+        <v>-3.6156</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2861</v>
+        <v>2.2301</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7426</v>
+        <v>-0.2736</v>
       </c>
       <c r="K19" t="n">
-        <v>0.08450000000000001</v>
+        <v>-2.2649</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6581</v>
+        <v>1.9913</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3838</v>
+        <v>-1.1119</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2442</v>
+        <v>-1.3507</v>
       </c>
       <c r="O19" t="n">
-        <v>0.628</v>
+        <v>0.2388</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3774</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3774</v>
+        <v>2.8305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8788</v>
+        <v>0.6737</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4115</v>
+        <v>0.2068</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4673</v>
+        <v>0.4669</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.1696</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.4714</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PUJALTE MIRA</t>
+          <t>J. GARCIA CORBI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2353</v>
+        <v>0.3811</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.707</v>
+        <v>0.2229</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9423</v>
+        <v>0.1582</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.124</v>
+        <v>-0.1628</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1902</v>
+        <v>-0.2927</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3142</v>
+        <v>0.1299</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1276</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7927999999999999</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6651</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2516</v>
+        <v>-0.1628</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6026</v>
+        <v>-0.2927</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.649</v>
+        <v>0.1299</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="S20" t="n">
-        <v>1.114</v>
+        <v>0.0533</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4296</v>
+        <v>-0.0789</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6843</v>
+        <v>0.1323</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3208</v>
+        <v>0.3018</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3208</v>
+        <v>0.3018</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. GARCIA CORBI</t>
+          <t>A. VAICIUNAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2043</v>
+        <v>0.0562</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1254</v>
+        <v>-2.9929</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0788</v>
+        <v>3.0492</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1628</v>
+        <v>1.1829</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2927</v>
+        <v>-0.205</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1299</v>
+        <v>1.3879</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.9035</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.7716</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.1319</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1628</v>
+        <v>0.2793</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2927</v>
+        <v>-0.9767</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1299</v>
+        <v>1.256</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1887</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1887</v>
+        <v>2.0757</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1235</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1764</v>
+        <v>-0.1225</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0529</v>
+        <v>0.0336</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3018</v>
+        <v>0.6606</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.6606</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. VAICIUNAS</t>
+          <t>J. PUJALTE MIRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5679</v>
+        <v>-0.1448</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0904</v>
+        <v>-0.9019</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5224</v>
+        <v>0.7571</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1829</v>
+        <v>-1.124</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.205</v>
+        <v>0.1902</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3879</v>
+        <v>-1.3142</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9035</v>
+        <v>0.1276</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7716</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1319</v>
+        <v>-0.6651</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2793</v>
+        <v>-1.2516</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9767</v>
+        <v>-0.6026</v>
       </c>
       <c r="O22" t="n">
-        <v>1.256</v>
+        <v>-0.649</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6983</v>
+        <v>0.5661</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0757</v>
+        <v>1.5096</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7131</v>
+        <v>0.7339</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2199</v>
+        <v>0.2348</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4932</v>
+        <v>0.4992</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6606</v>
+        <v>-0.3208</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6606</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0157</v>
+        <v>-2.3517</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7273</v>
+        <v>-2.1427</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2884</v>
+        <v>-0.209</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7619</v>
@@ -2248,13 +2248,13 @@
         <v>1.3209</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0082</v>
+        <v>-0.3442</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6343</v>
+        <v>-0.0497</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3738</v>
+        <v>-0.2945</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6795</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.763099999999999</v>
+        <v>9.062100000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.545700000000001</v>
+        <v>-3.5457</v>
       </c>
       <c r="F24" t="n">
-        <v>11.3086</v>
+        <v>12.6078</v>
       </c>
       <c r="G24" t="n">
-        <v>2.3826</v>
+        <v>2.382599999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.9484</v>
+        <v>-1.948400000000001</v>
       </c>
       <c r="I24" t="n">
         <v>4.331300000000001</v>
@@ -2302,13 +2302,13 @@
         <v>6.4301</v>
       </c>
       <c r="K24" t="n">
-        <v>5.783200000000001</v>
+        <v>5.783199999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6469999999999997</v>
+        <v>0.6469999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.0474</v>
+        <v>-4.047400000000001</v>
       </c>
       <c r="N24" t="n">
         <v>-7.731999999999999</v>
@@ -2317,7 +2317,7 @@
         <v>3.6844</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9434999999999998</v>
+        <v>-0.9434999999999996</v>
       </c>
       <c r="Q24" t="n">
         <v>-17.9265</v>
@@ -2326,19 +2326,19 @@
         <v>16.983</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7585000000000002</v>
+        <v>2.0575</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3120999999999999</v>
+        <v>-0.3122</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0705</v>
+        <v>2.3698</v>
       </c>
       <c r="V24" t="n">
-        <v>5.565499999999999</v>
+        <v>5.5655</v>
       </c>
       <c r="W24" t="n">
-        <v>8.262699999999999</v>
+        <v>8.262700000000002</v>
       </c>
       <c r="X24" t="n">
         <v>-2.6972</v>
